--- a/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2FFA3447-2C94-4A44-879F-E4A88537C954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{090374D9-24D8-483A-B9E5-CE2C02006783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D4C4E1CA-BA6E-4026-92FE-8499E6C6119F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9692247E-D145-440D-A215-D5ED4D50A3B4}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2416,7 +2416,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4909C1CF-C162-470A-93F9-765ACCEA178F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06EDCB5C-0C45-490E-BF83-D4265F012739}">
   <dimension ref="B3:L283"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{090374D9-24D8-483A-B9E5-CE2C02006783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{18664DCC-B96E-4FB7-BB8F-294979F8B2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9692247E-D145-440D-A215-D5ED4D50A3B4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F1FCF3EF-C3F0-428F-BCA4-4E877E2CAC5A}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -68,1513 +71,1513 @@
     <t>ELC</t>
   </si>
   <si>
-    <t>e_PL1-400</t>
-  </si>
-  <si>
-    <t>e_w86494356-400</t>
-  </si>
-  <si>
-    <t>g_PL1-400-w86494356-400</t>
+    <t>e_PL1-400_POL</t>
+  </si>
+  <si>
+    <t>e_w86494356-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL1-400_POL-w86494356-400_POL</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>e_PL10-400</t>
-  </si>
-  <si>
-    <t>e_w32036484-400</t>
-  </si>
-  <si>
-    <t>g_PL10-400-w32036484-400</t>
-  </si>
-  <si>
-    <t>e_w32943179-400</t>
-  </si>
-  <si>
-    <t>g_PL10-400-w32943179-400</t>
-  </si>
-  <si>
-    <t>e_PL11-220</t>
-  </si>
-  <si>
-    <t>e_w39428977-220</t>
-  </si>
-  <si>
-    <t>g_PL11-220-w39428977-220</t>
-  </si>
-  <si>
-    <t>e_PL13-400</t>
-  </si>
-  <si>
-    <t>e_w46235456-400</t>
-  </si>
-  <si>
-    <t>g_PL13-400-w46235456-400</t>
-  </si>
-  <si>
-    <t>e_PL14-220</t>
-  </si>
-  <si>
-    <t>e_PL22-220</t>
-  </si>
-  <si>
-    <t>g_PL14-220-PL22-220</t>
-  </si>
-  <si>
-    <t>e_PL14-400</t>
-  </si>
-  <si>
-    <t>g_PL14-400-PL13-400</t>
-  </si>
-  <si>
-    <t>e_PL15-400</t>
-  </si>
-  <si>
-    <t>g_PL15-400-PL14-400</t>
-  </si>
-  <si>
-    <t>e_PL17-400</t>
-  </si>
-  <si>
-    <t>e_w293489663-400</t>
-  </si>
-  <si>
-    <t>g_PL17-400-w293489663-400</t>
-  </si>
-  <si>
-    <t>e_PL20-220</t>
-  </si>
-  <si>
-    <t>e_w121656686-220</t>
-  </si>
-  <si>
-    <t>g_PL20-220-w121656686-220</t>
-  </si>
-  <si>
-    <t>e_PL21-220</t>
-  </si>
-  <si>
-    <t>e_w171992870-220</t>
-  </si>
-  <si>
-    <t>g_PL21-220-w171992870-220</t>
-  </si>
-  <si>
-    <t>e_w29115701-220</t>
-  </si>
-  <si>
-    <t>g_PL21-220-w29115701-220</t>
-  </si>
-  <si>
-    <t>e_PL23-400</t>
-  </si>
-  <si>
-    <t>g_PL23-400-PL17-400</t>
-  </si>
-  <si>
-    <t>e_PL24-220</t>
-  </si>
-  <si>
-    <t>e_w25898810-220</t>
-  </si>
-  <si>
-    <t>g_PL24-220-w25898810-220</t>
-  </si>
-  <si>
-    <t>e_w99593626-220</t>
-  </si>
-  <si>
-    <t>g_PL24-220-w99593626-220</t>
-  </si>
-  <si>
-    <t>e_PL25-220</t>
-  </si>
-  <si>
-    <t>e_w254938713-220</t>
-  </si>
-  <si>
-    <t>g_PL25-220-w254938713-220</t>
-  </si>
-  <si>
-    <t>e_PL25-400</t>
-  </si>
-  <si>
-    <t>e_w254938713-400</t>
-  </si>
-  <si>
-    <t>g_PL25-400-w254938713-400</t>
-  </si>
-  <si>
-    <t>e_PL26-400</t>
-  </si>
-  <si>
-    <t>g_PL26-400-PL23-400</t>
-  </si>
-  <si>
-    <t>e_w255973806-400</t>
-  </si>
-  <si>
-    <t>g_PL26-400-w255973806-400</t>
-  </si>
-  <si>
-    <t>e_PL27-400</t>
-  </si>
-  <si>
-    <t>g_PL27-400-PL26-400</t>
-  </si>
-  <si>
-    <t>e_PL28-400</t>
-  </si>
-  <si>
-    <t>e_w99593626-400</t>
-  </si>
-  <si>
-    <t>g_PL28-400-w99593626-400</t>
-  </si>
-  <si>
-    <t>e_PL29-400</t>
-  </si>
-  <si>
-    <t>g_PL29-400-PL26-400</t>
-  </si>
-  <si>
-    <t>g_PL29-400-PL27-400</t>
-  </si>
-  <si>
-    <t>e_PL31-400</t>
-  </si>
-  <si>
-    <t>g_PL31-400-PL28-400</t>
-  </si>
-  <si>
-    <t>e_PL32-220</t>
-  </si>
-  <si>
-    <t>e_PL33-220</t>
-  </si>
-  <si>
-    <t>g_PL32-220-PL33-220</t>
-  </si>
-  <si>
-    <t>e_w189851841-220</t>
-  </si>
-  <si>
-    <t>g_PL33-220-w189851841-220</t>
-  </si>
-  <si>
-    <t>e_PL34-400</t>
-  </si>
-  <si>
-    <t>e_w79033485-400</t>
-  </si>
-  <si>
-    <t>g_PL34-400-w79033485-400</t>
-  </si>
-  <si>
-    <t>e_PL35-220</t>
-  </si>
-  <si>
-    <t>e_PL42-220</t>
-  </si>
-  <si>
-    <t>g_PL35-220-PL42-220</t>
-  </si>
-  <si>
-    <t>e_PL36-400</t>
-  </si>
-  <si>
-    <t>e_PL41-400</t>
-  </si>
-  <si>
-    <t>g_PL36-400-PL41-400</t>
-  </si>
-  <si>
-    <t>e_PL38-400</t>
-  </si>
-  <si>
-    <t>e_w154510504-400</t>
-  </si>
-  <si>
-    <t>g_PL38-400-w154510504-400</t>
-  </si>
-  <si>
-    <t>e_PL39-220</t>
-  </si>
-  <si>
-    <t>e_PL37-220</t>
-  </si>
-  <si>
-    <t>g_PL39-220-PL37-220</t>
-  </si>
-  <si>
-    <t>e_PL4-220</t>
-  </si>
-  <si>
-    <t>e_PL8-220</t>
-  </si>
-  <si>
-    <t>g_PL4-220-PL8-220</t>
-  </si>
-  <si>
-    <t>e_PL40-220</t>
-  </si>
-  <si>
-    <t>e_w111615226-220</t>
-  </si>
-  <si>
-    <t>g_PL40-220-w111615226-220</t>
-  </si>
-  <si>
-    <t>e_PL40-400</t>
-  </si>
-  <si>
-    <t>e_w111615226-400</t>
-  </si>
-  <si>
-    <t>g_PL40-400-w111615226-400</t>
-  </si>
-  <si>
-    <t>e_w241842600-400</t>
-  </si>
-  <si>
-    <t>g_PL41-400-w241842600-400</t>
-  </si>
-  <si>
-    <t>e_w241842600-220</t>
-  </si>
-  <si>
-    <t>g_PL42-220-w241842600-220</t>
-  </si>
-  <si>
-    <t>e_PL43-220</t>
-  </si>
-  <si>
-    <t>e_PL44-220</t>
-  </si>
-  <si>
-    <t>g_PL43-220-PL44-220</t>
-  </si>
-  <si>
-    <t>g_PL43-220-w241842600-220</t>
-  </si>
-  <si>
-    <t>e_w224727316-220</t>
-  </si>
-  <si>
-    <t>g_PL44-220-w224727316-220</t>
-  </si>
-  <si>
-    <t>e_PL45-220</t>
-  </si>
-  <si>
-    <t>g_PL45-220-PL43-220</t>
-  </si>
-  <si>
-    <t>e_w66161634-220</t>
-  </si>
-  <si>
-    <t>g_PL45-220-w66161634-220</t>
-  </si>
-  <si>
-    <t>e_PL46-220</t>
-  </si>
-  <si>
-    <t>e_w179279860-220</t>
-  </si>
-  <si>
-    <t>g_PL46-220-w179279860-220</t>
-  </si>
-  <si>
-    <t>e_w336990960-220</t>
-  </si>
-  <si>
-    <t>g_PL46-220-w336990960-220</t>
-  </si>
-  <si>
-    <t>e_PL47-220</t>
-  </si>
-  <si>
-    <t>e_w199098050-220</t>
-  </si>
-  <si>
-    <t>g_PL47-220-w199098050-220</t>
-  </si>
-  <si>
-    <t>e_PL48-220</t>
-  </si>
-  <si>
-    <t>e_w191352746-220</t>
-  </si>
-  <si>
-    <t>g_PL48-220-w191352746-220</t>
-  </si>
-  <si>
-    <t>e_PL49-220</t>
-  </si>
-  <si>
-    <t>g_PL49-220-PL39-220</t>
-  </si>
-  <si>
-    <t>e_PL5-220</t>
-  </si>
-  <si>
-    <t>g_PL5-220-PL4-220</t>
-  </si>
-  <si>
-    <t>e_w40062974-220</t>
-  </si>
-  <si>
-    <t>g_PL5-220-w40062974-220</t>
-  </si>
-  <si>
-    <t>e_PL51-400</t>
-  </si>
-  <si>
-    <t>g_PL51-400-w241842600-400</t>
-  </si>
-  <si>
-    <t>e_w40946784-400</t>
-  </si>
-  <si>
-    <t>g_PL51-400-w40946784-400</t>
-  </si>
-  <si>
-    <t>e_PL52-400</t>
-  </si>
-  <si>
-    <t>g_PL52-400-PL51-400</t>
-  </si>
-  <si>
-    <t>e_w66161634-400</t>
-  </si>
-  <si>
-    <t>g_PL52-400-w66161634-400</t>
-  </si>
-  <si>
-    <t>e_PL53-220</t>
-  </si>
-  <si>
-    <t>e_w40946790-220</t>
-  </si>
-  <si>
-    <t>g_PL53-220-w40946790-220</t>
-  </si>
-  <si>
-    <t>e_w66051759-220</t>
-  </si>
-  <si>
-    <t>g_PL53-220-w66051759-220</t>
-  </si>
-  <si>
-    <t>e_PL55-220</t>
-  </si>
-  <si>
-    <t>e_PL56-220</t>
-  </si>
-  <si>
-    <t>g_PL55-220-PL56-220</t>
-  </si>
-  <si>
-    <t>e_PL58-220</t>
-  </si>
-  <si>
-    <t>g_PL55-220-PL58-220</t>
-  </si>
-  <si>
-    <t>e_PL57-220</t>
-  </si>
-  <si>
-    <t>g_PL56-220-PL57-220</t>
-  </si>
-  <si>
-    <t>e_w133537926-220</t>
-  </si>
-  <si>
-    <t>g_PL57-220-w133537926-220</t>
-  </si>
-  <si>
-    <t>e_w183259405-220</t>
-  </si>
-  <si>
-    <t>g_PL58-220-w183259405-220</t>
-  </si>
-  <si>
-    <t>e_PL59-220</t>
-  </si>
-  <si>
-    <t>e_w139452056-220</t>
-  </si>
-  <si>
-    <t>g_PL59-220-w139452056-220</t>
-  </si>
-  <si>
-    <t>e_PL61-220</t>
-  </si>
-  <si>
-    <t>g_PL61-220-PL49-220</t>
-  </si>
-  <si>
-    <t>e_PL62-400</t>
-  </si>
-  <si>
-    <t>e_w215282393-400</t>
-  </si>
-  <si>
-    <t>g_PL62-400-w215282393-400</t>
-  </si>
-  <si>
-    <t>e_PL7-400</t>
-  </si>
-  <si>
-    <t>e_w46092396-400</t>
-  </si>
-  <si>
-    <t>g_PL7-400-w46092396-400</t>
-  </si>
-  <si>
-    <t>e_w32943179-220</t>
-  </si>
-  <si>
-    <t>g_PL8-220-w32943179-220</t>
-  </si>
-  <si>
-    <t>e_r18085709-400</t>
-  </si>
-  <si>
-    <t>g_r18085709-400-w86494356-400</t>
-  </si>
-  <si>
-    <t>e_r9399771-220</t>
-  </si>
-  <si>
-    <t>e_PL50-220</t>
-  </si>
-  <si>
-    <t>g_r9399771-220-PL50-220</t>
-  </si>
-  <si>
-    <t>e_w87667718-220</t>
-  </si>
-  <si>
-    <t>g_r9399771-220-w87667718-220</t>
-  </si>
-  <si>
-    <t>e_w101914781-220</t>
-  </si>
-  <si>
-    <t>e_w101915790-220</t>
-  </si>
-  <si>
-    <t>g_w101914781-220-w101915790-220</t>
-  </si>
-  <si>
-    <t>e_w101982559-220</t>
-  </si>
-  <si>
-    <t>e_w35366436-220</t>
-  </si>
-  <si>
-    <t>g_w101982559-220-w35366436-220</t>
-  </si>
-  <si>
-    <t>e_w102165724-220</t>
-  </si>
-  <si>
-    <t>g_w102165724-220-w35366436-220</t>
-  </si>
-  <si>
-    <t>e_w1022342082-220</t>
-  </si>
-  <si>
-    <t>g_w1022342082-220-PL20-220</t>
-  </si>
-  <si>
-    <t>e_w1022342082-400</t>
-  </si>
-  <si>
-    <t>e_w121656686-400</t>
-  </si>
-  <si>
-    <t>g_w1022342082-400-w121656686-400</t>
-  </si>
-  <si>
-    <t>g_w1022342082-400-w255973806-400</t>
-  </si>
-  <si>
-    <t>e_w158232924-220</t>
-  </si>
-  <si>
-    <t>g_w111615226-220-w158232924-220</t>
-  </si>
-  <si>
-    <t>e_w178756295-220</t>
-  </si>
-  <si>
-    <t>g_w111615226-220-w178756295-220</t>
-  </si>
-  <si>
-    <t>e_w180542657-220</t>
-  </si>
-  <si>
-    <t>g_w111615226-220-w180542657-220</t>
-  </si>
-  <si>
-    <t>e_w276291999-220</t>
-  </si>
-  <si>
-    <t>g_w111615226-220-w276291999-220</t>
-  </si>
-  <si>
-    <t>g_w111615226-400-PL34-400</t>
-  </si>
-  <si>
-    <t>e_w112614319-400</t>
-  </si>
-  <si>
-    <t>e_w101914781-400</t>
-  </si>
-  <si>
-    <t>g_w112614319-400-w101914781-400</t>
-  </si>
-  <si>
-    <t>e_w130644710-400</t>
-  </si>
-  <si>
-    <t>g_w112614319-400-w130644710-400</t>
-  </si>
-  <si>
-    <t>g_w112614319-400-w46092396-400</t>
-  </si>
-  <si>
-    <t>e_w115801644-220</t>
-  </si>
-  <si>
-    <t>g_w115801644-220-w87667718-220</t>
-  </si>
-  <si>
-    <t>g_w121656686-220-w101915790-220</t>
-  </si>
-  <si>
-    <t>e_w170259740-220</t>
-  </si>
-  <si>
-    <t>g_w121656686-220-w170259740-220</t>
-  </si>
-  <si>
-    <t>e_PL16-400</t>
-  </si>
-  <si>
-    <t>g_w121656686-400-PL16-400</t>
-  </si>
-  <si>
-    <t>g_w121656686-400-w101914781-400</t>
-  </si>
-  <si>
-    <t>e_w255972326-400</t>
-  </si>
-  <si>
-    <t>g_w121656686-400-w255972326-400</t>
-  </si>
-  <si>
-    <t>e_w130644710-220</t>
-  </si>
-  <si>
-    <t>e_PL2-220</t>
-  </si>
-  <si>
-    <t>g_w130644710-220-PL2-220</t>
-  </si>
-  <si>
-    <t>e_w534238983-220</t>
-  </si>
-  <si>
-    <t>g_w130644710-220-w534238983-220</t>
-  </si>
-  <si>
-    <t>g_w130644710-400-w86494356-400</t>
-  </si>
-  <si>
-    <t>e_w131120723-220</t>
-  </si>
-  <si>
-    <t>g_w131120723-220-PL25-220</t>
-  </si>
-  <si>
-    <t>g_w133537926-220-PL53-220</t>
-  </si>
-  <si>
-    <t>e_PL54-220</t>
-  </si>
-  <si>
-    <t>g_w133537926-220-PL54-220</t>
-  </si>
-  <si>
-    <t>g_w133537926-220-PL57-220</t>
-  </si>
-  <si>
-    <t>g_w133537926-220-r9399771-220</t>
-  </si>
-  <si>
-    <t>e_w189501431-220</t>
-  </si>
-  <si>
-    <t>g_w133537926-220-w189501431-220</t>
-  </si>
-  <si>
-    <t>e_w133537926-400</t>
-  </si>
-  <si>
-    <t>e_PL54-400</t>
-  </si>
-  <si>
-    <t>g_w133537926-400-PL54-400</t>
-  </si>
-  <si>
-    <t>e_w189501431-400</t>
-  </si>
-  <si>
-    <t>g_w133537926-400-w189501431-400</t>
-  </si>
-  <si>
-    <t>g_w133537926-400-w40946784-400</t>
-  </si>
-  <si>
-    <t>e_w135598292-220</t>
-  </si>
-  <si>
-    <t>g_w135598292-220-w133537926-220</t>
-  </si>
-  <si>
-    <t>g_w139452056-220-PL59-220</t>
-  </si>
-  <si>
-    <t>e_w183945016-220</t>
-  </si>
-  <si>
-    <t>g_w139452056-220-w183945016-220</t>
-  </si>
-  <si>
-    <t>e_w184899160-220</t>
-  </si>
-  <si>
-    <t>g_w139452056-220-w184899160-220</t>
-  </si>
-  <si>
-    <t>e_w139452056-400</t>
-  </si>
-  <si>
-    <t>e_PL59-400</t>
-  </si>
-  <si>
-    <t>g_w139452056-400-PL59-400</t>
-  </si>
-  <si>
-    <t>e_w293489607-400</t>
-  </si>
-  <si>
-    <t>g_w139452056-400-w293489607-400</t>
-  </si>
-  <si>
-    <t>e_w143484238-220</t>
-  </si>
-  <si>
-    <t>e_PL6-220</t>
-  </si>
-  <si>
-    <t>g_w143484238-220-PL6-220</t>
-  </si>
-  <si>
-    <t>e_w72879943-220</t>
-  </si>
-  <si>
-    <t>g_w143484238-220-w72879943-220</t>
-  </si>
-  <si>
-    <t>e_w144646702-400</t>
-  </si>
-  <si>
-    <t>e_w251239544-400</t>
-  </si>
-  <si>
-    <t>g_w144646702-400-w251239544-400</t>
-  </si>
-  <si>
-    <t>e_w658600169-400</t>
-  </si>
-  <si>
-    <t>g_w144646702-400-w658600169-400</t>
-  </si>
-  <si>
-    <t>e_w145037309-220</t>
-  </si>
-  <si>
-    <t>e_w251239544-220</t>
-  </si>
-  <si>
-    <t>g_w145037309-220-w251239544-220</t>
-  </si>
-  <si>
-    <t>e_w148060965-400</t>
-  </si>
-  <si>
-    <t>e_w194903381-400</t>
-  </si>
-  <si>
-    <t>g_w148060965-400-w194903381-400</t>
-  </si>
-  <si>
-    <t>e_w148197330-220</t>
-  </si>
-  <si>
-    <t>e_w32036484-220</t>
-  </si>
-  <si>
-    <t>g_w148197330-220-w32036484-220</t>
-  </si>
-  <si>
-    <t>e_w153838553-220</t>
-  </si>
-  <si>
-    <t>g_w153838553-220-PL47-220</t>
-  </si>
-  <si>
-    <t>g_w153838553-220-PL50-220</t>
-  </si>
-  <si>
-    <t>e_w154894455-400</t>
-  </si>
-  <si>
-    <t>g_w154894455-400-PL34-400</t>
-  </si>
-  <si>
-    <t>e_w180542657-400</t>
-  </si>
-  <si>
-    <t>g_w154894455-400-w180542657-400</t>
-  </si>
-  <si>
-    <t>e_PL30-220</t>
-  </si>
-  <si>
-    <t>g_w158232924-220-PL30-220</t>
-  </si>
-  <si>
-    <t>e_w180535363-220</t>
-  </si>
-  <si>
-    <t>g_w158232924-220-w180535363-220</t>
-  </si>
-  <si>
-    <t>e_w165763717-220</t>
-  </si>
-  <si>
-    <t>g_w165763717-220-PL5-220</t>
-  </si>
-  <si>
-    <t>e_w166710856-400</t>
-  </si>
-  <si>
-    <t>e_w166838338-400</t>
-  </si>
-  <si>
-    <t>g_w166710856-400-w166838338-400</t>
-  </si>
-  <si>
-    <t>e_w199098053-400</t>
-  </si>
-  <si>
-    <t>g_w166710856-400-w199098053-400</t>
-  </si>
-  <si>
-    <t>g_w166710856-400-w215282393-400</t>
-  </si>
-  <si>
-    <t>g_w166838338-400-PL62-400</t>
-  </si>
-  <si>
-    <t>e_w170249563-220</t>
-  </si>
-  <si>
-    <t>e_w170368942-220</t>
-  </si>
-  <si>
-    <t>g_w170249563-220-w170368942-220</t>
-  </si>
-  <si>
-    <t>e_w173613665-220</t>
-  </si>
-  <si>
-    <t>g_w170368942-220-w173613665-220</t>
-  </si>
-  <si>
-    <t>e_w194903381-220</t>
-  </si>
-  <si>
-    <t>g_w170368942-220-w194903381-220</t>
-  </si>
-  <si>
-    <t>e_w171383831-220</t>
-  </si>
-  <si>
-    <t>g_w171383831-220-w101982559-220</t>
-  </si>
-  <si>
-    <t>g_w171383831-220-w102165724-220</t>
-  </si>
-  <si>
-    <t>e_w171917072-400</t>
-  </si>
-  <si>
-    <t>g_w171917072-400-PL41-400</t>
-  </si>
-  <si>
-    <t>e_w293484891-400</t>
-  </si>
-  <si>
-    <t>g_w171917072-400-w293484891-400</t>
-  </si>
-  <si>
-    <t>e_w681264796-400</t>
-  </si>
-  <si>
-    <t>g_w171917072-400-w681264796-400</t>
-  </si>
-  <si>
-    <t>e_w173582810-220</t>
-  </si>
-  <si>
-    <t>g_w173582810-220-PL32-220</t>
-  </si>
-  <si>
-    <t>e_w88544449-220</t>
-  </si>
-  <si>
-    <t>g_w173582810-220-w88544449-220</t>
-  </si>
-  <si>
-    <t>e_w173582810-400</t>
-  </si>
-  <si>
-    <t>g_w173582810-400-PL29-400</t>
-  </si>
-  <si>
-    <t>g_w173582810-400-PL31-400</t>
-  </si>
-  <si>
-    <t>g_w173582810-400-w148060965-400</t>
-  </si>
-  <si>
-    <t>e_w175406958-220</t>
-  </si>
-  <si>
-    <t>e_w178838661-220</t>
-  </si>
-  <si>
-    <t>g_w175406958-220-w178838661-220</t>
-  </si>
-  <si>
-    <t>e_w175406958-400</t>
-  </si>
-  <si>
-    <t>g_w175406958-400-r18085709-400</t>
-  </si>
-  <si>
-    <t>e_w177749653-220</t>
-  </si>
-  <si>
-    <t>g_w177749653-220-w276291999-220</t>
-  </si>
-  <si>
-    <t>g_w178756295-220-w177749653-220</t>
-  </si>
-  <si>
-    <t>g_w178838661-220-w534238983-220</t>
-  </si>
-  <si>
-    <t>e_w178838661-400</t>
-  </si>
-  <si>
-    <t>e_w534238983-400</t>
-  </si>
-  <si>
-    <t>g_w178838661-400-w534238983-400</t>
-  </si>
-  <si>
-    <t>g_w180535363-220-w180542657-220</t>
-  </si>
-  <si>
-    <t>g_w180542657-220-w148197330-220</t>
-  </si>
-  <si>
-    <t>g_w180542657-220-w32036484-220</t>
-  </si>
-  <si>
-    <t>g_w183945016-220-PL58-220</t>
-  </si>
-  <si>
-    <t>e_w291375946-220</t>
-  </si>
-  <si>
-    <t>g_w184899160-220-w291375946-220</t>
-  </si>
-  <si>
-    <t>e_w185454704-220</t>
-  </si>
-  <si>
-    <t>g_w185454704-220-w139452056-220</t>
-  </si>
-  <si>
-    <t>g_w185454704-220-w66161634-220</t>
-  </si>
-  <si>
-    <t>e_w185459155-220</t>
-  </si>
-  <si>
-    <t>g_w185459155-220-w139452056-220</t>
-  </si>
-  <si>
-    <t>g_w189501431-220-w115801644-220</t>
-  </si>
-  <si>
-    <t>e_w191035265-220</t>
-  </si>
-  <si>
-    <t>g_w189501431-220-w191035265-220</t>
-  </si>
-  <si>
-    <t>g_w189501431-400-w166710856-400</t>
-  </si>
-  <si>
-    <t>g_w189501431-400-w215282393-400</t>
-  </si>
-  <si>
-    <t>g_w189851841-220-w88544449-220</t>
-  </si>
-  <si>
-    <t>e_PL60-220</t>
-  </si>
-  <si>
-    <t>g_w191035265-220-PL60-220</t>
-  </si>
-  <si>
-    <t>e_w191038569-220</t>
-  </si>
-  <si>
-    <t>g_w191038569-220-w191035265-220</t>
-  </si>
-  <si>
-    <t>e_w198635989-220</t>
-  </si>
-  <si>
-    <t>g_w191352746-220-w198635989-220</t>
-  </si>
-  <si>
-    <t>e_w726776987-220</t>
-  </si>
-  <si>
-    <t>g_w191352746-220-w726776987-220</t>
-  </si>
-  <si>
-    <t>g_w199098050-220-w189851841-220</t>
-  </si>
-  <si>
-    <t>e_w199098055-220</t>
-  </si>
-  <si>
-    <t>g_w199098050-220-w199098055-220</t>
-  </si>
-  <si>
-    <t>e_w228154083-220</t>
-  </si>
-  <si>
-    <t>g_w199098050-220-w228154083-220</t>
-  </si>
-  <si>
-    <t>e_w199098050-400</t>
-  </si>
-  <si>
-    <t>g_w199098050-400-w199098053-400</t>
-  </si>
-  <si>
-    <t>e_w199098053-220</t>
-  </si>
-  <si>
-    <t>g_w199098053-220-PL48-220</t>
-  </si>
-  <si>
-    <t>g_w199098053-220-w191352746-220</t>
-  </si>
-  <si>
-    <t>e_w254235846-400</t>
-  </si>
-  <si>
-    <t>g_w199098053-400-w254235846-400</t>
-  </si>
-  <si>
-    <t>g_w199098055-220-PL48-220</t>
-  </si>
-  <si>
-    <t>g_w199098055-220-w228154083-220</t>
-  </si>
-  <si>
-    <t>g_w215282393-400-w199098053-400</t>
-  </si>
-  <si>
-    <t>e_w216060722-220</t>
-  </si>
-  <si>
-    <t>g_w216060722-220-PL42-220</t>
-  </si>
-  <si>
-    <t>e_w216975352-220</t>
-  </si>
-  <si>
-    <t>g_w216975352-220-w145037309-220</t>
-  </si>
-  <si>
-    <t>g_w216975352-220-w171383831-220</t>
-  </si>
-  <si>
-    <t>e_w217899005-220</t>
-  </si>
-  <si>
-    <t>g_w217899005-220-PL44-220</t>
-  </si>
-  <si>
-    <t>g_w217899005-220-PL45-220</t>
-  </si>
-  <si>
-    <t>e_w238640596-220</t>
-  </si>
-  <si>
-    <t>g_w238640596-220-w178838661-220</t>
-  </si>
-  <si>
-    <t>g_w238640596-220-w32036484-220</t>
-  </si>
-  <si>
-    <t>e_w238640596-400</t>
-  </si>
-  <si>
-    <t>g_w238640596-400-w32036484-400</t>
-  </si>
-  <si>
-    <t>g_w241842600-220-PL35-220</t>
-  </si>
-  <si>
-    <t>g_w241842600-220-PL47-220</t>
-  </si>
-  <si>
-    <t>g_w241842600-220-w199098050-220</t>
-  </si>
-  <si>
-    <t>g_w241842600-400-w293484891-400</t>
-  </si>
-  <si>
-    <t>e_w245964556-220</t>
-  </si>
-  <si>
-    <t>e_PL19-220</t>
-  </si>
-  <si>
-    <t>g_w245964556-220-PL19-220</t>
-  </si>
-  <si>
-    <t>g_w251239544-220-w29115701-220</t>
-  </si>
-  <si>
-    <t>e_w91384044-400</t>
-  </si>
-  <si>
-    <t>g_w251239544-400-w91384044-400</t>
-  </si>
-  <si>
-    <t>g_w251239544-400-w99593626-400</t>
-  </si>
-  <si>
-    <t>e_w254235846-220</t>
-  </si>
-  <si>
-    <t>g_w254235846-220-PL39-220</t>
-  </si>
-  <si>
-    <t>g_w254235846-400-w173582810-400</t>
-  </si>
-  <si>
-    <t>e_w255284259-400</t>
-  </si>
-  <si>
-    <t>g_w254938713-400-w255284259-400</t>
-  </si>
-  <si>
-    <t>e_w255293403-400</t>
-  </si>
-  <si>
-    <t>g_w254938713-400-w255293403-400</t>
-  </si>
-  <si>
-    <t>e_w255232597-220</t>
-  </si>
-  <si>
-    <t>g_w255232597-220-w133537926-220</t>
-  </si>
-  <si>
-    <t>e_w255277953-400</t>
-  </si>
-  <si>
-    <t>g_w255277953-400-PL36-400</t>
-  </si>
-  <si>
-    <t>g_w255277953-400-PL38-400</t>
-  </si>
-  <si>
-    <t>g_w255277953-400-w139452056-400</t>
-  </si>
-  <si>
-    <t>e_w255284259-220</t>
-  </si>
-  <si>
-    <t>g_w255284259-220-PL21-220</t>
-  </si>
-  <si>
-    <t>g_w255284259-220-PL22-220</t>
-  </si>
-  <si>
-    <t>g_w255284259-220-w216975352-220</t>
-  </si>
-  <si>
-    <t>g_w255284259-220-w72879943-220</t>
-  </si>
-  <si>
-    <t>g_w255284259-400-PL15-400</t>
-  </si>
-  <si>
-    <t>e_w255293400-220</t>
-  </si>
-  <si>
-    <t>g_w255293400-220-w238640596-220</t>
-  </si>
-  <si>
-    <t>e_w255293400-400</t>
-  </si>
-  <si>
-    <t>g_w255293400-400-PL15-400</t>
-  </si>
-  <si>
-    <t>g_w255293400-400-w238640596-400</t>
-  </si>
-  <si>
-    <t>g_w255293403-400-w171917072-400</t>
-  </si>
-  <si>
-    <t>g_w255293403-400-w293484891-400</t>
-  </si>
-  <si>
-    <t>g_w255972326-400-PL17-400</t>
-  </si>
-  <si>
-    <t>e_w303870256-400</t>
-  </si>
-  <si>
-    <t>g_w255972326-400-w303870256-400</t>
-  </si>
-  <si>
-    <t>e_w255972397-400</t>
-  </si>
-  <si>
-    <t>g_w255972397-400-PL27-400</t>
-  </si>
-  <si>
-    <t>e_w255973806-220</t>
-  </si>
-  <si>
-    <t>g_w255973806-220-PL20-220</t>
-  </si>
-  <si>
-    <t>g_w255973806-400-PL23-400</t>
-  </si>
-  <si>
-    <t>g_w276291999-220-PL46-220</t>
-  </si>
-  <si>
-    <t>e_w276291999-400</t>
-  </si>
-  <si>
-    <t>g_w276291999-400-w154510504-400</t>
-  </si>
-  <si>
-    <t>e_w29098336-220</t>
-  </si>
-  <si>
-    <t>g_w29098336-220-w173582810-220</t>
-  </si>
-  <si>
-    <t>g_w29115701-220-PL24-220</t>
-  </si>
-  <si>
-    <t>g_w29115701-220-w173582810-220</t>
-  </si>
-  <si>
-    <t>g_w29115701-220-w29098336-220</t>
-  </si>
-  <si>
-    <t>e_w89434732-220</t>
-  </si>
-  <si>
-    <t>g_w29115701-220-w89434732-220</t>
-  </si>
-  <si>
-    <t>g_w291375946-220-w135598292-220</t>
-  </si>
-  <si>
-    <t>e_w29139402-220</t>
-  </si>
-  <si>
-    <t>g_w29139402-220-PL55-220</t>
-  </si>
-  <si>
-    <t>e_w293484891-220</t>
-  </si>
-  <si>
-    <t>g_w293484891-220-PL35-220</t>
-  </si>
-  <si>
-    <t>g_w293484891-220-w102165724-220</t>
-  </si>
-  <si>
-    <t>e_w155971668-220</t>
-  </si>
-  <si>
-    <t>g_w293484891-220-w155971668-220</t>
-  </si>
-  <si>
-    <t>e_w170316833-220</t>
-  </si>
-  <si>
-    <t>g_w293484891-220-w170316833-220</t>
-  </si>
-  <si>
-    <t>g_w293484891-220-w35366436-220</t>
-  </si>
-  <si>
-    <t>e_w681264796-220</t>
-  </si>
-  <si>
-    <t>g_w293484891-220-w681264796-220</t>
-  </si>
-  <si>
-    <t>g_w293484891-400-w144646702-400</t>
-  </si>
-  <si>
-    <t>g_w293484891-400-w251239544-400</t>
-  </si>
-  <si>
-    <t>g_w293484891-400-w681264796-400</t>
-  </si>
-  <si>
-    <t>e_w293484894-220</t>
-  </si>
-  <si>
-    <t>g_w293484894-220-w255284259-220</t>
-  </si>
-  <si>
-    <t>g_w293489607-400-PL52-400</t>
-  </si>
-  <si>
-    <t>g_w32036484-220-PL25-220</t>
-  </si>
-  <si>
-    <t>g_w32036484-220-w293484894-220</t>
-  </si>
-  <si>
-    <t>e_PL18-400</t>
-  </si>
-  <si>
-    <t>g_w32036484-400-PL18-400</t>
-  </si>
-  <si>
-    <t>g_w32036484-400-PL25-400</t>
-  </si>
-  <si>
-    <t>g_w32943179-400-w175406958-400</t>
-  </si>
-  <si>
-    <t>g_w336990960-220-w185459155-220</t>
-  </si>
-  <si>
-    <t>g_w35366436-220-w170316833-220</t>
-  </si>
-  <si>
-    <t>g_w35366436-220-w251239544-220</t>
-  </si>
-  <si>
-    <t>e_w385098015-400</t>
-  </si>
-  <si>
-    <t>e_w385118244-400</t>
-  </si>
-  <si>
-    <t>g_w385098015-400-w385118244-400</t>
-  </si>
-  <si>
-    <t>g_w385118244-400-w130644710-400</t>
-  </si>
-  <si>
-    <t>e_w385539724-220</t>
-  </si>
-  <si>
-    <t>g_w385539724-220-w158232924-220</t>
-  </si>
-  <si>
-    <t>g_w39428977-220-PL11-220</t>
-  </si>
-  <si>
-    <t>g_w39428977-220-w32943179-220</t>
-  </si>
-  <si>
-    <t>g_w39428977-220-w385539724-220</t>
-  </si>
-  <si>
-    <t>g_w39428977-220-w40062974-220</t>
-  </si>
-  <si>
-    <t>e_w39428977-400</t>
-  </si>
-  <si>
-    <t>g_w39428977-400-PL10-400</t>
-  </si>
-  <si>
-    <t>e_PL11-400</t>
-  </si>
-  <si>
-    <t>g_w39428977-400-PL11-400</t>
-  </si>
-  <si>
-    <t>g_w39428977-400-PL18-400</t>
-  </si>
-  <si>
-    <t>g_w40946784-400-w189501431-400</t>
-  </si>
-  <si>
-    <t>e_w44389929-220</t>
-  </si>
-  <si>
-    <t>g_w44389929-220-w133537926-220</t>
-  </si>
-  <si>
-    <t>g_w46092396-400-w144646702-400</t>
-  </si>
-  <si>
-    <t>g_w46092396-400-w385098015-400</t>
-  </si>
-  <si>
-    <t>e_w46235456-220</t>
-  </si>
-  <si>
-    <t>e_PL13-220</t>
-  </si>
-  <si>
-    <t>g_w46235456-220-PL13-220</t>
-  </si>
-  <si>
-    <t>g_w46235456-220-PL22-220</t>
-  </si>
-  <si>
-    <t>e_PL3-220</t>
-  </si>
-  <si>
-    <t>g_w46235456-220-PL3-220</t>
-  </si>
-  <si>
-    <t>e_w46092396-220</t>
-  </si>
-  <si>
-    <t>g_w46235456-220-w46092396-220</t>
-  </si>
-  <si>
-    <t>g_w46235456-400-PL13-400</t>
-  </si>
-  <si>
-    <t>g_w46235456-400-PL7-400</t>
-  </si>
-  <si>
-    <t>g_w534238983-400-r18085709-400</t>
-  </si>
-  <si>
-    <t>g_w534238983-400-w385118244-400</t>
-  </si>
-  <si>
-    <t>g_w66051759-220-PL50-220</t>
-  </si>
-  <si>
-    <t>g_w66161634-220-w29139402-220</t>
-  </si>
-  <si>
-    <t>g_w66161634-220-w40946790-220</t>
-  </si>
-  <si>
-    <t>e_w668348943-220</t>
-  </si>
-  <si>
-    <t>g_w668348943-220-PL4-220</t>
-  </si>
-  <si>
-    <t>g_w668348943-220-PL8-220</t>
-  </si>
-  <si>
-    <t>g_w681264796-220-w293484891-220</t>
-  </si>
-  <si>
-    <t>g_w681264796-400-w293484891-400</t>
-  </si>
-  <si>
-    <t>g_w726776987-220-w170249563-220</t>
-  </si>
-  <si>
-    <t>g_w72879943-220-w101915790-220</t>
-  </si>
-  <si>
-    <t>g_w72879943-220-w245964556-220</t>
-  </si>
-  <si>
-    <t>g_w79033485-400-PL36-400</t>
-  </si>
-  <si>
-    <t>g_w79033485-400-PL38-400</t>
-  </si>
-  <si>
-    <t>g_w79033485-400-w255293403-400</t>
-  </si>
-  <si>
-    <t>g_w87667718-220-w191035265-220</t>
-  </si>
-  <si>
-    <t>g_w88544449-220-w170249563-220</t>
-  </si>
-  <si>
-    <t>g_w91384044-400-w99593626-400</t>
-  </si>
-  <si>
-    <t>e_w98611253-220</t>
-  </si>
-  <si>
-    <t>g_w98611253-220-w44389929-220</t>
-  </si>
-  <si>
-    <t>e_w98634956-220</t>
-  </si>
-  <si>
-    <t>g_w98634956-220-w255232597-220</t>
-  </si>
-  <si>
-    <t>g_w98634956-220-w44389929-220</t>
-  </si>
-  <si>
-    <t>g_w99593626-220-w255973806-220</t>
-  </si>
-  <si>
-    <t>g_w99593626-400-w255973806-400</t>
+    <t>e_PL10-400_POL</t>
+  </si>
+  <si>
+    <t>e_w32036484-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL10-400_POL-w32036484-400_POL</t>
+  </si>
+  <si>
+    <t>e_w32943179-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL10-400_POL-w32943179-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL11-220_POL</t>
+  </si>
+  <si>
+    <t>e_w39428977-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL11-220_POL-w39428977-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL13-400_POL</t>
+  </si>
+  <si>
+    <t>e_w46235456-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL13-400_POL-w46235456-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL14-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL22-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL14-220_POL-PL22-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL14-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL14-400_POL-PL13-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL15-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL15-400_POL-PL14-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL17-400_POL</t>
+  </si>
+  <si>
+    <t>e_w293489663-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL17-400_POL-w293489663-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL20-220_POL</t>
+  </si>
+  <si>
+    <t>e_w121656686-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL20-220_POL-w121656686-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL21-220_POL</t>
+  </si>
+  <si>
+    <t>e_w171992870-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL21-220_POL-w171992870-220_POL</t>
+  </si>
+  <si>
+    <t>e_w29115701-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL21-220_POL-w29115701-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL23-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL23-400_POL-PL17-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL24-220_POL</t>
+  </si>
+  <si>
+    <t>e_w25898810-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL24-220_POL-w25898810-220_POL</t>
+  </si>
+  <si>
+    <t>e_w99593626-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL24-220_POL-w99593626-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL25-220_POL</t>
+  </si>
+  <si>
+    <t>e_w254938713-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL25-220_POL-w254938713-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL25-400_POL</t>
+  </si>
+  <si>
+    <t>e_w254938713-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL25-400_POL-w254938713-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL26-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL26-400_POL-PL23-400_POL</t>
+  </si>
+  <si>
+    <t>e_w255973806-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL26-400_POL-w255973806-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL27-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL27-400_POL-PL26-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL28-400_POL</t>
+  </si>
+  <si>
+    <t>e_w99593626-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL28-400_POL-w99593626-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL29-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL29-400_POL-PL26-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL29-400_POL-PL27-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL31-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL31-400_POL-PL28-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL32-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL33-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL32-220_POL-PL33-220_POL</t>
+  </si>
+  <si>
+    <t>e_w189851841-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL33-220_POL-w189851841-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL34-400_POL</t>
+  </si>
+  <si>
+    <t>e_w79033485-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL34-400_POL-w79033485-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL35-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL42-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL35-220_POL-PL42-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL36-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL41-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL36-400_POL-PL41-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL38-400_POL</t>
+  </si>
+  <si>
+    <t>e_w154510504-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL38-400_POL-w154510504-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL39-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL37-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL39-220_POL-PL37-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL4-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL8-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL4-220_POL-PL8-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL40-220_POL</t>
+  </si>
+  <si>
+    <t>e_w111615226-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL40-220_POL-w111615226-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL40-400_POL</t>
+  </si>
+  <si>
+    <t>e_w111615226-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL40-400_POL-w111615226-400_POL</t>
+  </si>
+  <si>
+    <t>e_w241842600-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL41-400_POL-w241842600-400_POL</t>
+  </si>
+  <si>
+    <t>e_w241842600-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL42-220_POL-w241842600-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL43-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL44-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL43-220_POL-PL44-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL43-220_POL-w241842600-220_POL</t>
+  </si>
+  <si>
+    <t>e_w224727316-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL44-220_POL-w224727316-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL45-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL45-220_POL-PL43-220_POL</t>
+  </si>
+  <si>
+    <t>e_w66161634-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL45-220_POL-w66161634-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL46-220_POL</t>
+  </si>
+  <si>
+    <t>e_w179279860-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL46-220_POL-w179279860-220_POL</t>
+  </si>
+  <si>
+    <t>e_w336990960-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL46-220_POL-w336990960-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL47-220_POL</t>
+  </si>
+  <si>
+    <t>e_w199098050-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL47-220_POL-w199098050-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL48-220_POL</t>
+  </si>
+  <si>
+    <t>e_w191352746-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL48-220_POL-w191352746-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL49-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL49-220_POL-PL39-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL5-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL5-220_POL-PL4-220_POL</t>
+  </si>
+  <si>
+    <t>e_w40062974-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL5-220_POL-w40062974-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL51-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL51-400_POL-w241842600-400_POL</t>
+  </si>
+  <si>
+    <t>e_w40946784-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL51-400_POL-w40946784-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL52-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL52-400_POL-PL51-400_POL</t>
+  </si>
+  <si>
+    <t>e_w66161634-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL52-400_POL-w66161634-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL53-220_POL</t>
+  </si>
+  <si>
+    <t>e_w40946790-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL53-220_POL-w40946790-220_POL</t>
+  </si>
+  <si>
+    <t>e_w66051759-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL53-220_POL-w66051759-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL55-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL56-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL55-220_POL-PL56-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL58-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL55-220_POL-PL58-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL57-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL56-220_POL-PL57-220_POL</t>
+  </si>
+  <si>
+    <t>e_w133537926-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL57-220_POL-w133537926-220_POL</t>
+  </si>
+  <si>
+    <t>e_w183259405-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL58-220_POL-w183259405-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL59-220_POL</t>
+  </si>
+  <si>
+    <t>e_w139452056-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL59-220_POL-w139452056-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL61-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL61-220_POL-PL49-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL62-400_POL</t>
+  </si>
+  <si>
+    <t>e_w215282393-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL62-400_POL-w215282393-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL7-400_POL</t>
+  </si>
+  <si>
+    <t>e_w46092396-400_POL</t>
+  </si>
+  <si>
+    <t>g_PL7-400_POL-w46092396-400_POL</t>
+  </si>
+  <si>
+    <t>e_w32943179-220_POL</t>
+  </si>
+  <si>
+    <t>g_PL8-220_POL-w32943179-220_POL</t>
+  </si>
+  <si>
+    <t>e_r18085709-400_POL</t>
+  </si>
+  <si>
+    <t>g_r18085709-400_POL-w86494356-400_POL</t>
+  </si>
+  <si>
+    <t>e_r9399771-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL50-220_POL</t>
+  </si>
+  <si>
+    <t>g_r9399771-220_POL-PL50-220_POL</t>
+  </si>
+  <si>
+    <t>e_w87667718-220_POL</t>
+  </si>
+  <si>
+    <t>g_r9399771-220_POL-w87667718-220_POL</t>
+  </si>
+  <si>
+    <t>e_w101914781-220_POL</t>
+  </si>
+  <si>
+    <t>e_w101915790-220_POL</t>
+  </si>
+  <si>
+    <t>g_w101914781-220_POL-w101915790-220_POL</t>
+  </si>
+  <si>
+    <t>e_w101982559-220_POL</t>
+  </si>
+  <si>
+    <t>e_w35366436-220_POL</t>
+  </si>
+  <si>
+    <t>g_w101982559-220_POL-w35366436-220_POL</t>
+  </si>
+  <si>
+    <t>e_w102165724-220_POL</t>
+  </si>
+  <si>
+    <t>g_w102165724-220_POL-w35366436-220_POL</t>
+  </si>
+  <si>
+    <t>e_w1022342082-220_POL</t>
+  </si>
+  <si>
+    <t>g_w1022342082-220_POL-PL20-220_POL</t>
+  </si>
+  <si>
+    <t>e_w1022342082-400_POL</t>
+  </si>
+  <si>
+    <t>e_w121656686-400_POL</t>
+  </si>
+  <si>
+    <t>g_w1022342082-400_POL-w121656686-400_POL</t>
+  </si>
+  <si>
+    <t>g_w1022342082-400_POL-w255973806-400_POL</t>
+  </si>
+  <si>
+    <t>e_w158232924-220_POL</t>
+  </si>
+  <si>
+    <t>g_w111615226-220_POL-w158232924-220_POL</t>
+  </si>
+  <si>
+    <t>e_w178756295-220_POL</t>
+  </si>
+  <si>
+    <t>g_w111615226-220_POL-w178756295-220_POL</t>
+  </si>
+  <si>
+    <t>e_w180542657-220_POL</t>
+  </si>
+  <si>
+    <t>g_w111615226-220_POL-w180542657-220_POL</t>
+  </si>
+  <si>
+    <t>e_w276291999-220_POL</t>
+  </si>
+  <si>
+    <t>g_w111615226-220_POL-w276291999-220_POL</t>
+  </si>
+  <si>
+    <t>g_w111615226-400_POL-PL34-400_POL</t>
+  </si>
+  <si>
+    <t>e_w112614319-400_POL</t>
+  </si>
+  <si>
+    <t>e_w101914781-400_POL</t>
+  </si>
+  <si>
+    <t>g_w112614319-400_POL-w101914781-400_POL</t>
+  </si>
+  <si>
+    <t>e_w130644710-400_POL</t>
+  </si>
+  <si>
+    <t>g_w112614319-400_POL-w130644710-400_POL</t>
+  </si>
+  <si>
+    <t>g_w112614319-400_POL-w46092396-400_POL</t>
+  </si>
+  <si>
+    <t>e_w115801644-220_POL</t>
+  </si>
+  <si>
+    <t>g_w115801644-220_POL-w87667718-220_POL</t>
+  </si>
+  <si>
+    <t>g_w121656686-220_POL-w101915790-220_POL</t>
+  </si>
+  <si>
+    <t>e_w170259740-220_POL</t>
+  </si>
+  <si>
+    <t>g_w121656686-220_POL-w170259740-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL16-400_POL</t>
+  </si>
+  <si>
+    <t>g_w121656686-400_POL-PL16-400_POL</t>
+  </si>
+  <si>
+    <t>g_w121656686-400_POL-w101914781-400_POL</t>
+  </si>
+  <si>
+    <t>e_w255972326-400_POL</t>
+  </si>
+  <si>
+    <t>g_w121656686-400_POL-w255972326-400_POL</t>
+  </si>
+  <si>
+    <t>e_w130644710-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL2-220_POL</t>
+  </si>
+  <si>
+    <t>g_w130644710-220_POL-PL2-220_POL</t>
+  </si>
+  <si>
+    <t>e_w534238983-220_POL</t>
+  </si>
+  <si>
+    <t>g_w130644710-220_POL-w534238983-220_POL</t>
+  </si>
+  <si>
+    <t>g_w130644710-400_POL-w86494356-400_POL</t>
+  </si>
+  <si>
+    <t>e_w131120723-220_POL</t>
+  </si>
+  <si>
+    <t>g_w131120723-220_POL-PL25-220_POL</t>
+  </si>
+  <si>
+    <t>g_w133537926-220_POL-PL53-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL54-220_POL</t>
+  </si>
+  <si>
+    <t>g_w133537926-220_POL-PL54-220_POL</t>
+  </si>
+  <si>
+    <t>g_w133537926-220_POL-PL57-220_POL</t>
+  </si>
+  <si>
+    <t>g_w133537926-220_POL-r9399771-220_POL</t>
+  </si>
+  <si>
+    <t>e_w189501431-220_POL</t>
+  </si>
+  <si>
+    <t>g_w133537926-220_POL-w189501431-220_POL</t>
+  </si>
+  <si>
+    <t>e_w133537926-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL54-400_POL</t>
+  </si>
+  <si>
+    <t>g_w133537926-400_POL-PL54-400_POL</t>
+  </si>
+  <si>
+    <t>e_w189501431-400_POL</t>
+  </si>
+  <si>
+    <t>g_w133537926-400_POL-w189501431-400_POL</t>
+  </si>
+  <si>
+    <t>g_w133537926-400_POL-w40946784-400_POL</t>
+  </si>
+  <si>
+    <t>e_w135598292-220_POL</t>
+  </si>
+  <si>
+    <t>g_w135598292-220_POL-w133537926-220_POL</t>
+  </si>
+  <si>
+    <t>g_w139452056-220_POL-PL59-220_POL</t>
+  </si>
+  <si>
+    <t>e_w183945016-220_POL</t>
+  </si>
+  <si>
+    <t>g_w139452056-220_POL-w183945016-220_POL</t>
+  </si>
+  <si>
+    <t>e_w184899160-220_POL</t>
+  </si>
+  <si>
+    <t>g_w139452056-220_POL-w184899160-220_POL</t>
+  </si>
+  <si>
+    <t>e_w139452056-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL59-400_POL</t>
+  </si>
+  <si>
+    <t>g_w139452056-400_POL-PL59-400_POL</t>
+  </si>
+  <si>
+    <t>e_w293489607-400_POL</t>
+  </si>
+  <si>
+    <t>g_w139452056-400_POL-w293489607-400_POL</t>
+  </si>
+  <si>
+    <t>e_w143484238-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL6-220_POL</t>
+  </si>
+  <si>
+    <t>g_w143484238-220_POL-PL6-220_POL</t>
+  </si>
+  <si>
+    <t>e_w72879943-220_POL</t>
+  </si>
+  <si>
+    <t>g_w143484238-220_POL-w72879943-220_POL</t>
+  </si>
+  <si>
+    <t>e_w144646702-400_POL</t>
+  </si>
+  <si>
+    <t>e_w251239544-400_POL</t>
+  </si>
+  <si>
+    <t>g_w144646702-400_POL-w251239544-400_POL</t>
+  </si>
+  <si>
+    <t>e_w658600169-400_POL</t>
+  </si>
+  <si>
+    <t>g_w144646702-400_POL-w658600169-400_POL</t>
+  </si>
+  <si>
+    <t>e_w145037309-220_POL</t>
+  </si>
+  <si>
+    <t>e_w251239544-220_POL</t>
+  </si>
+  <si>
+    <t>g_w145037309-220_POL-w251239544-220_POL</t>
+  </si>
+  <si>
+    <t>e_w148060965-400_POL</t>
+  </si>
+  <si>
+    <t>e_w194903381-400_POL</t>
+  </si>
+  <si>
+    <t>g_w148060965-400_POL-w194903381-400_POL</t>
+  </si>
+  <si>
+    <t>e_w148197330-220_POL</t>
+  </si>
+  <si>
+    <t>e_w32036484-220_POL</t>
+  </si>
+  <si>
+    <t>g_w148197330-220_POL-w32036484-220_POL</t>
+  </si>
+  <si>
+    <t>e_w153838553-220_POL</t>
+  </si>
+  <si>
+    <t>g_w153838553-220_POL-PL47-220_POL</t>
+  </si>
+  <si>
+    <t>g_w153838553-220_POL-PL50-220_POL</t>
+  </si>
+  <si>
+    <t>e_w154894455-400_POL</t>
+  </si>
+  <si>
+    <t>g_w154894455-400_POL-PL34-400_POL</t>
+  </si>
+  <si>
+    <t>e_w180542657-400_POL</t>
+  </si>
+  <si>
+    <t>g_w154894455-400_POL-w180542657-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL30-220_POL</t>
+  </si>
+  <si>
+    <t>g_w158232924-220_POL-PL30-220_POL</t>
+  </si>
+  <si>
+    <t>e_w180535363-220_POL</t>
+  </si>
+  <si>
+    <t>g_w158232924-220_POL-w180535363-220_POL</t>
+  </si>
+  <si>
+    <t>e_w165763717-220_POL</t>
+  </si>
+  <si>
+    <t>g_w165763717-220_POL-PL5-220_POL</t>
+  </si>
+  <si>
+    <t>e_w166710856-400_POL</t>
+  </si>
+  <si>
+    <t>e_w166838338-400_POL</t>
+  </si>
+  <si>
+    <t>g_w166710856-400_POL-w166838338-400_POL</t>
+  </si>
+  <si>
+    <t>e_w199098053-400_POL</t>
+  </si>
+  <si>
+    <t>g_w166710856-400_POL-w199098053-400_POL</t>
+  </si>
+  <si>
+    <t>g_w166710856-400_POL-w215282393-400_POL</t>
+  </si>
+  <si>
+    <t>g_w166838338-400_POL-PL62-400_POL</t>
+  </si>
+  <si>
+    <t>e_w170249563-220_POL</t>
+  </si>
+  <si>
+    <t>e_w170368942-220_POL</t>
+  </si>
+  <si>
+    <t>g_w170249563-220_POL-w170368942-220_POL</t>
+  </si>
+  <si>
+    <t>e_w173613665-220_POL</t>
+  </si>
+  <si>
+    <t>g_w170368942-220_POL-w173613665-220_POL</t>
+  </si>
+  <si>
+    <t>e_w194903381-220_POL</t>
+  </si>
+  <si>
+    <t>g_w170368942-220_POL-w194903381-220_POL</t>
+  </si>
+  <si>
+    <t>e_w171383831-220_POL</t>
+  </si>
+  <si>
+    <t>g_w171383831-220_POL-w101982559-220_POL</t>
+  </si>
+  <si>
+    <t>g_w171383831-220_POL-w102165724-220_POL</t>
+  </si>
+  <si>
+    <t>e_w171917072-400_POL</t>
+  </si>
+  <si>
+    <t>g_w171917072-400_POL-PL41-400_POL</t>
+  </si>
+  <si>
+    <t>e_w293484891-400_POL</t>
+  </si>
+  <si>
+    <t>g_w171917072-400_POL-w293484891-400_POL</t>
+  </si>
+  <si>
+    <t>e_w681264796-400_POL</t>
+  </si>
+  <si>
+    <t>g_w171917072-400_POL-w681264796-400_POL</t>
+  </si>
+  <si>
+    <t>e_w173582810-220_POL</t>
+  </si>
+  <si>
+    <t>g_w173582810-220_POL-PL32-220_POL</t>
+  </si>
+  <si>
+    <t>e_w88544449-220_POL</t>
+  </si>
+  <si>
+    <t>g_w173582810-220_POL-w88544449-220_POL</t>
+  </si>
+  <si>
+    <t>e_w173582810-400_POL</t>
+  </si>
+  <si>
+    <t>g_w173582810-400_POL-PL29-400_POL</t>
+  </si>
+  <si>
+    <t>g_w173582810-400_POL-PL31-400_POL</t>
+  </si>
+  <si>
+    <t>g_w173582810-400_POL-w148060965-400_POL</t>
+  </si>
+  <si>
+    <t>e_w175406958-220_POL</t>
+  </si>
+  <si>
+    <t>e_w178838661-220_POL</t>
+  </si>
+  <si>
+    <t>g_w175406958-220_POL-w178838661-220_POL</t>
+  </si>
+  <si>
+    <t>e_w175406958-400_POL</t>
+  </si>
+  <si>
+    <t>g_w175406958-400_POL-r18085709-400_POL</t>
+  </si>
+  <si>
+    <t>e_w177749653-220_POL</t>
+  </si>
+  <si>
+    <t>g_w177749653-220_POL-w276291999-220_POL</t>
+  </si>
+  <si>
+    <t>g_w178756295-220_POL-w177749653-220_POL</t>
+  </si>
+  <si>
+    <t>g_w178838661-220_POL-w534238983-220_POL</t>
+  </si>
+  <si>
+    <t>e_w178838661-400_POL</t>
+  </si>
+  <si>
+    <t>e_w534238983-400_POL</t>
+  </si>
+  <si>
+    <t>g_w178838661-400_POL-w534238983-400_POL</t>
+  </si>
+  <si>
+    <t>g_w180535363-220_POL-w180542657-220_POL</t>
+  </si>
+  <si>
+    <t>g_w180542657-220_POL-w148197330-220_POL</t>
+  </si>
+  <si>
+    <t>g_w180542657-220_POL-w32036484-220_POL</t>
+  </si>
+  <si>
+    <t>g_w183945016-220_POL-PL58-220_POL</t>
+  </si>
+  <si>
+    <t>e_w291375946-220_POL</t>
+  </si>
+  <si>
+    <t>g_w184899160-220_POL-w291375946-220_POL</t>
+  </si>
+  <si>
+    <t>e_w185454704-220_POL</t>
+  </si>
+  <si>
+    <t>g_w185454704-220_POL-w139452056-220_POL</t>
+  </si>
+  <si>
+    <t>g_w185454704-220_POL-w66161634-220_POL</t>
+  </si>
+  <si>
+    <t>e_w185459155-220_POL</t>
+  </si>
+  <si>
+    <t>g_w185459155-220_POL-w139452056-220_POL</t>
+  </si>
+  <si>
+    <t>g_w189501431-220_POL-w115801644-220_POL</t>
+  </si>
+  <si>
+    <t>e_w191035265-220_POL</t>
+  </si>
+  <si>
+    <t>g_w189501431-220_POL-w191035265-220_POL</t>
+  </si>
+  <si>
+    <t>g_w189501431-400_POL-w166710856-400_POL</t>
+  </si>
+  <si>
+    <t>g_w189501431-400_POL-w215282393-400_POL</t>
+  </si>
+  <si>
+    <t>g_w189851841-220_POL-w88544449-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL60-220_POL</t>
+  </si>
+  <si>
+    <t>g_w191035265-220_POL-PL60-220_POL</t>
+  </si>
+  <si>
+    <t>e_w191038569-220_POL</t>
+  </si>
+  <si>
+    <t>g_w191038569-220_POL-w191035265-220_POL</t>
+  </si>
+  <si>
+    <t>e_w198635989-220_POL</t>
+  </si>
+  <si>
+    <t>g_w191352746-220_POL-w198635989-220_POL</t>
+  </si>
+  <si>
+    <t>e_w726776987-220_POL</t>
+  </si>
+  <si>
+    <t>g_w191352746-220_POL-w726776987-220_POL</t>
+  </si>
+  <si>
+    <t>g_w199098050-220_POL-w189851841-220_POL</t>
+  </si>
+  <si>
+    <t>e_w199098055-220_POL</t>
+  </si>
+  <si>
+    <t>g_w199098050-220_POL-w199098055-220_POL</t>
+  </si>
+  <si>
+    <t>e_w228154083-220_POL</t>
+  </si>
+  <si>
+    <t>g_w199098050-220_POL-w228154083-220_POL</t>
+  </si>
+  <si>
+    <t>e_w199098050-400_POL</t>
+  </si>
+  <si>
+    <t>g_w199098050-400_POL-w199098053-400_POL</t>
+  </si>
+  <si>
+    <t>e_w199098053-220_POL</t>
+  </si>
+  <si>
+    <t>g_w199098053-220_POL-PL48-220_POL</t>
+  </si>
+  <si>
+    <t>g_w199098053-220_POL-w191352746-220_POL</t>
+  </si>
+  <si>
+    <t>e_w254235846-400_POL</t>
+  </si>
+  <si>
+    <t>g_w199098053-400_POL-w254235846-400_POL</t>
+  </si>
+  <si>
+    <t>g_w199098055-220_POL-PL48-220_POL</t>
+  </si>
+  <si>
+    <t>g_w199098055-220_POL-w228154083-220_POL</t>
+  </si>
+  <si>
+    <t>g_w215282393-400_POL-w199098053-400_POL</t>
+  </si>
+  <si>
+    <t>e_w216060722-220_POL</t>
+  </si>
+  <si>
+    <t>g_w216060722-220_POL-PL42-220_POL</t>
+  </si>
+  <si>
+    <t>e_w216975352-220_POL</t>
+  </si>
+  <si>
+    <t>g_w216975352-220_POL-w145037309-220_POL</t>
+  </si>
+  <si>
+    <t>g_w216975352-220_POL-w171383831-220_POL</t>
+  </si>
+  <si>
+    <t>e_w217899005-220_POL</t>
+  </si>
+  <si>
+    <t>g_w217899005-220_POL-PL44-220_POL</t>
+  </si>
+  <si>
+    <t>g_w217899005-220_POL-PL45-220_POL</t>
+  </si>
+  <si>
+    <t>e_w238640596-220_POL</t>
+  </si>
+  <si>
+    <t>g_w238640596-220_POL-w178838661-220_POL</t>
+  </si>
+  <si>
+    <t>g_w238640596-220_POL-w32036484-220_POL</t>
+  </si>
+  <si>
+    <t>e_w238640596-400_POL</t>
+  </si>
+  <si>
+    <t>g_w238640596-400_POL-w32036484-400_POL</t>
+  </si>
+  <si>
+    <t>g_w241842600-220_POL-PL35-220_POL</t>
+  </si>
+  <si>
+    <t>g_w241842600-220_POL-PL47-220_POL</t>
+  </si>
+  <si>
+    <t>g_w241842600-220_POL-w199098050-220_POL</t>
+  </si>
+  <si>
+    <t>g_w241842600-400_POL-w293484891-400_POL</t>
+  </si>
+  <si>
+    <t>e_w245964556-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL19-220_POL</t>
+  </si>
+  <si>
+    <t>g_w245964556-220_POL-PL19-220_POL</t>
+  </si>
+  <si>
+    <t>g_w251239544-220_POL-w29115701-220_POL</t>
+  </si>
+  <si>
+    <t>e_w91384044-400_POL</t>
+  </si>
+  <si>
+    <t>g_w251239544-400_POL-w91384044-400_POL</t>
+  </si>
+  <si>
+    <t>g_w251239544-400_POL-w99593626-400_POL</t>
+  </si>
+  <si>
+    <t>e_w254235846-220_POL</t>
+  </si>
+  <si>
+    <t>g_w254235846-220_POL-PL39-220_POL</t>
+  </si>
+  <si>
+    <t>g_w254235846-400_POL-w173582810-400_POL</t>
+  </si>
+  <si>
+    <t>e_w255284259-400_POL</t>
+  </si>
+  <si>
+    <t>g_w254938713-400_POL-w255284259-400_POL</t>
+  </si>
+  <si>
+    <t>e_w255293403-400_POL</t>
+  </si>
+  <si>
+    <t>g_w254938713-400_POL-w255293403-400_POL</t>
+  </si>
+  <si>
+    <t>e_w255232597-220_POL</t>
+  </si>
+  <si>
+    <t>g_w255232597-220_POL-w133537926-220_POL</t>
+  </si>
+  <si>
+    <t>e_w255277953-400_POL</t>
+  </si>
+  <si>
+    <t>g_w255277953-400_POL-PL36-400_POL</t>
+  </si>
+  <si>
+    <t>g_w255277953-400_POL-PL38-400_POL</t>
+  </si>
+  <si>
+    <t>g_w255277953-400_POL-w139452056-400_POL</t>
+  </si>
+  <si>
+    <t>e_w255284259-220_POL</t>
+  </si>
+  <si>
+    <t>g_w255284259-220_POL-PL21-220_POL</t>
+  </si>
+  <si>
+    <t>g_w255284259-220_POL-PL22-220_POL</t>
+  </si>
+  <si>
+    <t>g_w255284259-220_POL-w216975352-220_POL</t>
+  </si>
+  <si>
+    <t>g_w255284259-220_POL-w72879943-220_POL</t>
+  </si>
+  <si>
+    <t>g_w255284259-400_POL-PL15-400_POL</t>
+  </si>
+  <si>
+    <t>e_w255293400-220_POL</t>
+  </si>
+  <si>
+    <t>g_w255293400-220_POL-w238640596-220_POL</t>
+  </si>
+  <si>
+    <t>e_w255293400-400_POL</t>
+  </si>
+  <si>
+    <t>g_w255293400-400_POL-PL15-400_POL</t>
+  </si>
+  <si>
+    <t>g_w255293400-400_POL-w238640596-400_POL</t>
+  </si>
+  <si>
+    <t>g_w255293403-400_POL-w171917072-400_POL</t>
+  </si>
+  <si>
+    <t>g_w255293403-400_POL-w293484891-400_POL</t>
+  </si>
+  <si>
+    <t>g_w255972326-400_POL-PL17-400_POL</t>
+  </si>
+  <si>
+    <t>e_w303870256-400_POL</t>
+  </si>
+  <si>
+    <t>g_w255972326-400_POL-w303870256-400_POL</t>
+  </si>
+  <si>
+    <t>e_w255972397-400_POL</t>
+  </si>
+  <si>
+    <t>g_w255972397-400_POL-PL27-400_POL</t>
+  </si>
+  <si>
+    <t>e_w255973806-220_POL</t>
+  </si>
+  <si>
+    <t>g_w255973806-220_POL-PL20-220_POL</t>
+  </si>
+  <si>
+    <t>g_w255973806-400_POL-PL23-400_POL</t>
+  </si>
+  <si>
+    <t>g_w276291999-220_POL-PL46-220_POL</t>
+  </si>
+  <si>
+    <t>e_w276291999-400_POL</t>
+  </si>
+  <si>
+    <t>g_w276291999-400_POL-w154510504-400_POL</t>
+  </si>
+  <si>
+    <t>e_w29098336-220_POL</t>
+  </si>
+  <si>
+    <t>g_w29098336-220_POL-w173582810-220_POL</t>
+  </si>
+  <si>
+    <t>g_w29115701-220_POL-PL24-220_POL</t>
+  </si>
+  <si>
+    <t>g_w29115701-220_POL-w173582810-220_POL</t>
+  </si>
+  <si>
+    <t>g_w29115701-220_POL-w29098336-220_POL</t>
+  </si>
+  <si>
+    <t>e_w89434732-220_POL</t>
+  </si>
+  <si>
+    <t>g_w29115701-220_POL-w89434732-220_POL</t>
+  </si>
+  <si>
+    <t>g_w291375946-220_POL-w135598292-220_POL</t>
+  </si>
+  <si>
+    <t>e_w29139402-220_POL</t>
+  </si>
+  <si>
+    <t>g_w29139402-220_POL-PL55-220_POL</t>
+  </si>
+  <si>
+    <t>e_w293484891-220_POL</t>
+  </si>
+  <si>
+    <t>g_w293484891-220_POL-PL35-220_POL</t>
+  </si>
+  <si>
+    <t>g_w293484891-220_POL-w102165724-220_POL</t>
+  </si>
+  <si>
+    <t>e_w155971668-220_POL</t>
+  </si>
+  <si>
+    <t>g_w293484891-220_POL-w155971668-220_POL</t>
+  </si>
+  <si>
+    <t>e_w170316833-220_POL</t>
+  </si>
+  <si>
+    <t>g_w293484891-220_POL-w170316833-220_POL</t>
+  </si>
+  <si>
+    <t>g_w293484891-220_POL-w35366436-220_POL</t>
+  </si>
+  <si>
+    <t>e_w681264796-220_POL</t>
+  </si>
+  <si>
+    <t>g_w293484891-220_POL-w681264796-220_POL</t>
+  </si>
+  <si>
+    <t>g_w293484891-400_POL-w144646702-400_POL</t>
+  </si>
+  <si>
+    <t>g_w293484891-400_POL-w251239544-400_POL</t>
+  </si>
+  <si>
+    <t>g_w293484891-400_POL-w681264796-400_POL</t>
+  </si>
+  <si>
+    <t>e_w293484894-220_POL</t>
+  </si>
+  <si>
+    <t>g_w293484894-220_POL-w255284259-220_POL</t>
+  </si>
+  <si>
+    <t>g_w293489607-400_POL-PL52-400_POL</t>
+  </si>
+  <si>
+    <t>g_w32036484-220_POL-PL25-220_POL</t>
+  </si>
+  <si>
+    <t>g_w32036484-220_POL-w293484894-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL18-400_POL</t>
+  </si>
+  <si>
+    <t>g_w32036484-400_POL-PL18-400_POL</t>
+  </si>
+  <si>
+    <t>g_w32036484-400_POL-PL25-400_POL</t>
+  </si>
+  <si>
+    <t>g_w32943179-400_POL-w175406958-400_POL</t>
+  </si>
+  <si>
+    <t>g_w336990960-220_POL-w185459155-220_POL</t>
+  </si>
+  <si>
+    <t>g_w35366436-220_POL-w170316833-220_POL</t>
+  </si>
+  <si>
+    <t>g_w35366436-220_POL-w251239544-220_POL</t>
+  </si>
+  <si>
+    <t>e_w385098015-400_POL</t>
+  </si>
+  <si>
+    <t>e_w385118244-400_POL</t>
+  </si>
+  <si>
+    <t>g_w385098015-400_POL-w385118244-400_POL</t>
+  </si>
+  <si>
+    <t>g_w385118244-400_POL-w130644710-400_POL</t>
+  </si>
+  <si>
+    <t>e_w385539724-220_POL</t>
+  </si>
+  <si>
+    <t>g_w385539724-220_POL-w158232924-220_POL</t>
+  </si>
+  <si>
+    <t>g_w39428977-220_POL-PL11-220_POL</t>
+  </si>
+  <si>
+    <t>g_w39428977-220_POL-w32943179-220_POL</t>
+  </si>
+  <si>
+    <t>g_w39428977-220_POL-w385539724-220_POL</t>
+  </si>
+  <si>
+    <t>g_w39428977-220_POL-w40062974-220_POL</t>
+  </si>
+  <si>
+    <t>e_w39428977-400_POL</t>
+  </si>
+  <si>
+    <t>g_w39428977-400_POL-PL10-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL11-400_POL</t>
+  </si>
+  <si>
+    <t>g_w39428977-400_POL-PL11-400_POL</t>
+  </si>
+  <si>
+    <t>g_w39428977-400_POL-PL18-400_POL</t>
+  </si>
+  <si>
+    <t>g_w40946784-400_POL-w189501431-400_POL</t>
+  </si>
+  <si>
+    <t>e_w44389929-220_POL</t>
+  </si>
+  <si>
+    <t>g_w44389929-220_POL-w133537926-220_POL</t>
+  </si>
+  <si>
+    <t>g_w46092396-400_POL-w144646702-400_POL</t>
+  </si>
+  <si>
+    <t>g_w46092396-400_POL-w385098015-400_POL</t>
+  </si>
+  <si>
+    <t>e_w46235456-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL13-220_POL</t>
+  </si>
+  <si>
+    <t>g_w46235456-220_POL-PL13-220_POL</t>
+  </si>
+  <si>
+    <t>g_w46235456-220_POL-PL22-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL3-220_POL</t>
+  </si>
+  <si>
+    <t>g_w46235456-220_POL-PL3-220_POL</t>
+  </si>
+  <si>
+    <t>e_w46092396-220_POL</t>
+  </si>
+  <si>
+    <t>g_w46235456-220_POL-w46092396-220_POL</t>
+  </si>
+  <si>
+    <t>g_w46235456-400_POL-PL13-400_POL</t>
+  </si>
+  <si>
+    <t>g_w46235456-400_POL-PL7-400_POL</t>
+  </si>
+  <si>
+    <t>g_w534238983-400_POL-r18085709-400_POL</t>
+  </si>
+  <si>
+    <t>g_w534238983-400_POL-w385118244-400_POL</t>
+  </si>
+  <si>
+    <t>g_w66051759-220_POL-PL50-220_POL</t>
+  </si>
+  <si>
+    <t>g_w66161634-220_POL-w29139402-220_POL</t>
+  </si>
+  <si>
+    <t>g_w66161634-220_POL-w40946790-220_POL</t>
+  </si>
+  <si>
+    <t>e_w668348943-220_POL</t>
+  </si>
+  <si>
+    <t>g_w668348943-220_POL-PL4-220_POL</t>
+  </si>
+  <si>
+    <t>g_w668348943-220_POL-PL8-220_POL</t>
+  </si>
+  <si>
+    <t>g_w681264796-220_POL-w293484891-220_POL</t>
+  </si>
+  <si>
+    <t>g_w681264796-400_POL-w293484891-400_POL</t>
+  </si>
+  <si>
+    <t>g_w726776987-220_POL-w170249563-220_POL</t>
+  </si>
+  <si>
+    <t>g_w72879943-220_POL-w101915790-220_POL</t>
+  </si>
+  <si>
+    <t>g_w72879943-220_POL-w245964556-220_POL</t>
+  </si>
+  <si>
+    <t>g_w79033485-400_POL-PL36-400_POL</t>
+  </si>
+  <si>
+    <t>g_w79033485-400_POL-PL38-400_POL</t>
+  </si>
+  <si>
+    <t>g_w79033485-400_POL-w255293403-400_POL</t>
+  </si>
+  <si>
+    <t>g_w87667718-220_POL-w191035265-220_POL</t>
+  </si>
+  <si>
+    <t>g_w88544449-220_POL-w170249563-220_POL</t>
+  </si>
+  <si>
+    <t>g_w91384044-400_POL-w99593626-400_POL</t>
+  </si>
+  <si>
+    <t>e_w98611253-220_POL</t>
+  </si>
+  <si>
+    <t>g_w98611253-220_POL-w44389929-220_POL</t>
+  </si>
+  <si>
+    <t>e_w98634956-220_POL</t>
+  </si>
+  <si>
+    <t>g_w98634956-220_POL-w255232597-220_POL</t>
+  </si>
+  <si>
+    <t>g_w98634956-220_POL-w44389929-220_POL</t>
+  </si>
+  <si>
+    <t>g_w99593626-220_POL-w255973806-220_POL</t>
+  </si>
+  <si>
+    <t>g_w99593626-400_POL-w255973806-400_POL</t>
   </si>
   <si>
     <t>~tradelinks_desc</t>
@@ -2416,7 +2419,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06EDCB5C-0C45-490E-BF83-D4265F012739}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0A4A15-A95E-4CCA-9576-35D569A6F5BF}">
   <dimension ref="B3:L283"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18664DCC-B96E-4FB7-BB8F-294979F8B2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6455DA1-E4A1-4296-BD36-59CFE2CCFE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F1FCF3EF-C3F0-428F-BCA4-4E877E2CAC5A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{343BC22E-FF92-468A-A3EF-89E5A4BFA660}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2419,7 +2419,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0A4A15-A95E-4CCA-9576-35D569A6F5BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9102F925-2F8C-4B7D-9691-3BA9D4F03052}">
   <dimension ref="B3:L283"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6455DA1-E4A1-4296-BD36-59CFE2CCFE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A792B24D-52AA-4110-A39E-9EFA9A060895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{343BC22E-FF92-468A-A3EF-89E5A4BFA660}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CC07B3F7-28BE-428D-B86E-B0947A696093}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2419,7 +2419,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9102F925-2F8C-4B7D-9691-3BA9D4F03052}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4A2EB1-0722-466B-B37D-177D29761E62}">
   <dimension ref="B3:L283"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A792B24D-52AA-4110-A39E-9EFA9A060895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{351E8966-15A3-40F2-9945-34E1C850A1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CC07B3F7-28BE-428D-B86E-B0947A696093}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{163FEDDA-95B1-4F7F-BC5B-2D89B5DDA47B}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2419,7 +2419,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4A2EB1-0722-466B-B37D-177D29761E62}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D091ED8-B02F-4054-9783-288AC4F43524}">
   <dimension ref="B3:L283"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76242389-AA14-47CD-910A-A4864B8CE710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FC30255-CE4B-40A1-929B-EA00715B3B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{646F7C1E-EFB2-46B3-BC3C-4746E5DFEE0B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FAB7C148-7558-4721-8900-3EA884EE9670}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2208,7 +2208,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71114BF2-FA4B-FED2-9073-4DCE1D26E727}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0946C677-AD01-232F-10F1-B905FA4C1960}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2559,7 +2559,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F94EA473-8DEC-474D-ACE6-1F958BD31F5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E60E34CC-DBFF-449F-B101-8BB7930C6CF6}">
   <dimension ref="A1:L283"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>

--- a/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD339E11-03FD-47B8-836B-5ABE509B8B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03F19DF2-4D0F-4482-ACB6-0D3A5FAC02A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{06FB0D80-5334-40F7-9E48-FAA8CC7754E1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7A4B0A29-B984-4D7C-A52D-E6994045FBFD}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2419,7 +2419,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0BA746-FBAF-4998-AADC-D1B3ECFCC376}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A792A44A-69F6-46DB-BE57-D980FF0BE3CA}">
   <dimension ref="B3:L283"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03F19DF2-4D0F-4482-ACB6-0D3A5FAC02A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C1A5B38-A738-40BC-9AC6-6AABF653E2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7A4B0A29-B984-4D7C-A52D-E6994045FBFD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2A3D3978-FE90-4F8A-BBF8-ADDBB61BAEDA}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2419,7 +2419,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A792A44A-69F6-46DB-BE57-D980FF0BE3CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2204BEA5-3A69-47EE-A65D-CD3E943BE2F5}">
   <dimension ref="B3:L283"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C1A5B38-A738-40BC-9AC6-6AABF653E2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17ACB1A7-EC7A-4C35-BF42-32A629316A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2A3D3978-FE90-4F8A-BBF8-ADDBB61BAEDA}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F15C29A9-E488-4637-AD48-556DFEC8F127}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2419,7 +2419,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2204BEA5-3A69-47EE-A65D-CD3E943BE2F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05CF0740-9684-4B05-B1E6-50A32EE02F49}">
   <dimension ref="B3:L283"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17ACB1A7-EC7A-4C35-BF42-32A629316A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7866ACB4-A337-4AD5-AC9E-4A2D770B0337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F15C29A9-E488-4637-AD48-556DFEC8F127}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5AC83E9A-1DF8-4C8B-84CC-F147B3165634}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2419,7 +2419,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05CF0740-9684-4B05-B1E6-50A32EE02F49}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC9AA1DE-EF74-4FB2-B8FC-0B54C19A5033}">
   <dimension ref="B3:L283"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
